--- a/data/trans_orig/IP07C08-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19689</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34336</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41511</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58982</t>
+          <t>59205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>73861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32379</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>28787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40085</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>27220</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>39490</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>55376</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30617</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14144</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>52823</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>32002</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>61942</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>54636</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>74331</t>
+          <t>74497</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>126536</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>105372</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>132332</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>211575</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>249789</t>
+          <t>249427</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>124980</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>154353</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>134902</t>
+          <t>134809</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>162628</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>306873</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>59487</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>84762</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34486</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44819</t>
+          <t>44451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>41423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76803</t>
+          <t>78144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31514</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11775</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43596</t>
+          <t>43775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>25497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>62,55%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>45759</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>33525</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33278</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>46158</t>
+          <t>46827</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>63044</t>
+          <t>63662</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27280</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>30047</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>52711</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>35371</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>43769</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>68692</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>89199</t>
+          <t>88182</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -12337,7 +12337,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>134506</t>
+          <t>134379</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>164330</t>
+          <t>163929</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>269592</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>310401</t>
+          <t>310286</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>245461</t>
+          <t>246755</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>285863</t>
+          <t>288349</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>20474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28785</t>
+          <t>28551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38358</t>
+          <t>37811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>54880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>57677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>20429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43536</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32733</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>83571</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>31993</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>41706</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40370</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>57261</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>78340</t>
+          <t>76273</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>46118</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>44373</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>85759</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>153574</t>
+          <t>154255</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>185605</t>
+          <t>185656</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>159736</t>
+          <t>160037</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>191912</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>324735</t>
+          <t>323165</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>367519</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>151444</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>114035</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>145438</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>244634</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>284899</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>85186</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
